--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="19">
   <si>
     <t>Area</t>
   </si>
@@ -29,7 +29,46 @@
     <t>Orientamento produttivo</t>
   </si>
   <si>
-    <t>N_all</t>
+    <t>Semi brado</t>
+  </si>
+  <si>
+    <t>Stabulato</t>
+  </si>
+  <si>
+    <t>La</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>LIM</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>Collezione faunistica - diversa da giardino zoologico</t>
+  </si>
+  <si>
+    <t>Collezione faunistica - rifugio per animali</t>
+  </si>
+  <si>
+    <t>Da riproduzione</t>
+  </si>
+  <si>
+    <t>Non dpa</t>
+  </si>
+  <si>
+    <t>Produzione da ingrasso</t>
+  </si>
+  <si>
+    <t>Collezione faunistica - giardino zoologico</t>
+  </si>
+  <si>
+    <t>Familiare</t>
   </si>
 </sst>
 </file>
@@ -96,14 +135,262 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
